--- a/docs/sales-cashflow.xlsx
+++ b/docs/sales-cashflow.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="51">
   <si>
     <t>DocFácil — Corridas de caja del módulo de ventas</t>
   </si>
@@ -168,6 +168,9 @@
   </si>
   <si>
     <t>Margen neto mensual mes 12</t>
+  </si>
+  <si>
+    <t>Pro</t>
   </si>
 </sst>
 </file>
@@ -700,22 +703,22 @@
       </c>
       <c r="B5" s="6">
         <f>Básico!B4</f>
-        <v>149</v>
+        <v>299</v>
       </c>
       <c r="C5" s="6">
         <f>Básico!F28</f>
-        <v>11260.46671875000175</v>
+        <v>20847.40734375000102</v>
       </c>
       <c r="D5" s="7">
         <f>Básico!F29</f>
-        <v>16890.70007812500262</v>
+        <v>31271.11101562499971</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="6">
         <f>Básico!F31</f>
-        <v>26133.90966438353644</v>
+        <v>55549.78061797807459</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -724,22 +727,22 @@
       </c>
       <c r="B6" s="6">
         <f>Profesional!B4</f>
-        <v>299</v>
+        <v>599</v>
       </c>
       <c r="C6" s="6">
         <f>Profesional!F28</f>
-        <v>20847.40734375000102</v>
+        <v>38295.35578125000757</v>
       </c>
       <c r="D6" s="7">
         <f>Profesional!F29</f>
-        <v>31271.11101562499971</v>
+        <v>57443.03367187501135</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="6">
         <f>Profesional!F31</f>
-        <v>55549.78061797807459</v>
+        <v>117446.94187899530516</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -748,22 +751,22 @@
       </c>
       <c r="B7" s="6">
         <f>Clínica!B4</f>
-        <v>599</v>
+        <v>1199</v>
       </c>
       <c r="C7" s="6">
         <f>Clínica!F28</f>
-        <v>40021.28859375001048</v>
+        <v>71465.31984375001048</v>
       </c>
       <c r="D7" s="7">
         <f>Clínica!F29</f>
-        <v>60031.93289062501572</v>
+        <v>107197.97976562501572</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="6">
         <f>Clínica!F31</f>
-        <v>114381.52252516712178</v>
+        <v>244306.68375485797878</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -872,7 +875,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>149</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -894,7 +897,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>447</v>
+        <v>897</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -909,7 +912,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>223.5</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -924,7 +927,7 @@
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>223.5</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -948,7 +951,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1003,30 +1006,30 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>4358.25</v>
+        <v>8745.75</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
-        <v>-585</v>
+        <v>-877.5</v>
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-2931.75</v>
+        <v>-5586.75</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-2931.75</v>
+        <v>-5586.75</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1047,31 +1050,31 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>8607.54374999999891</v>
+        <v>17272.85625000000073</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
-        <v>-1155.375</v>
+        <v>-1733.0625</v>
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-5957.83125000000109</v>
+        <v>-11370.20624999999927</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-8889.58125000000109</v>
+        <v>-16956.95624999999927</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1092,31 +1095,31 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>12750.60515624999971</v>
+        <v>25586.78484374999607</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
-        <v>-1711.49062499999991</v>
+        <v>-2567.23593749999964</v>
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-2370.88546875000065</v>
+        <v>-3890.45109375000175</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-11260.46671875000175</v>
+        <v>-20847.40734375000102</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1137,31 +1140,31 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>16790.090027343747352</v>
+        <v>33692.86522265624808</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
-        <v>-2253.70335937499976</v>
+        <v>-3380.55503906249987</v>
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>1126.38666796874713</v>
+        <v>3402.31018359374866</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-10134.080050781254613</v>
+        <v>-17445.097160156252357</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1182,31 +1185,31 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>20728.58777666015521</v>
+        <v>41596.29359208983806</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
-        <v>-2782.36077539062489</v>
+        <v>-4173.54116308593711</v>
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>4536.22700126952986</v>
+        <v>10512.75242900390003</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>-5597.85304951172475</v>
+        <v>-6932.34473115235232</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1227,31 +1230,31 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>24568.62308224364824</v>
+        <v>49302.13625228759338</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
-        <v>-3297.80175600585881</v>
+        <v>-4946.70263400878866</v>
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>7860.82132623779034</v>
+        <v>17445.4336182788029</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>2262.9682767260656</v>
+        <v>10513.088887126450572</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1272,31 +1275,31 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>28312.65750518755885</v>
+        <v>56815.33284598040336</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
-        <v>-3800.35671210571263</v>
+        <v>-5700.53506815856872</v>
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>11102.30079308184577</v>
+        <v>24204.79777782183373</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>13365.26906980791136</v>
+        <v>34717.88666494828067</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1317,31 +1320,31 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>31963.091067557870701</v>
+        <v>64140.69952483088855</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
-        <v>-4290.34779430306935</v>
+        <v>-6435.52169145460448</v>
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>14262.74327325480044</v>
+        <v>30795.17783337628498</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>27628.012343062713626</v>
+        <v>65513.064498324565648</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1362,31 +1365,31 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>35522.26379086892121</v>
+        <v>71282.93203671011725</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
-        <v>-4768.089099445493048</v>
+        <v>-7152.13364916823866</v>
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>17344.17469142342816</v>
+        <v>37220.79838754187949</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>44972.18703448613815</v>
+        <v>102733.86288586644514</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1407,31 +1410,31 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>38992.45719609719526</v>
+        <v>78246.6087357923534</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
-        <v>-5233.88687195935563</v>
+        <v>-7850.83030793903254</v>
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>20348.570324137836</v>
+        <v>43485.77842785332177</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>65320.75735862397414</v>
+        <v>146219.64131371976691</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1452,31 +1455,31 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>42375.89576619477157</v>
+        <v>85036.19351739755075</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
-        <v>-5688.039700160371467</v>
+        <v>-8532.059550240557655</v>
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>23277.85606603440101</v>
+        <v>49594.13396715698764</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>88598.61342465836788</v>
+        <v>195813.77528087675455</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1497,31 +1500,31 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>45674.74837203989591</v>
+        <v>91656.038679462610162</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
-        <v>-6130.8387076563622</v>
+        <v>-9196.25806148454285</v>
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-6705</v>
+        <v>-13455</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-13410</v>
+        <v>-26910</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>26133.90966438353644</v>
+        <v>55549.78061797807459</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>114732.52308904190431</v>
+        <v>251363.55589885482914</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1535,7 +1538,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>11260.46671875000175</v>
+        <v>20847.40734375000102</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1544,7 +1547,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>16890.70007812500262</v>
+        <v>31271.11101562499971</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1553,7 +1556,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>45674.74837203989591</v>
+        <v>91656.038679462610162</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1562,7 +1565,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>26133.90966438353644</v>
+        <v>55549.78061797807459</v>
       </c>
     </row>
   </sheetData>
@@ -1615,7 +1618,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>29</v>
@@ -1626,7 +1629,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>299</v>
+        <v>599</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -1648,7 +1651,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>897</v>
+        <v>1797</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1663,7 +1666,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>448.5</v>
+        <v>898.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1678,7 +1681,7 @@
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>448.5</v>
+        <v>898.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1702,7 +1705,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1757,30 +1760,30 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>8745.75</v>
+        <v>17520.75</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
-        <v>-877.5</v>
+        <v>-1170</v>
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-5586.75</v>
+        <v>-10604.25</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-5586.75</v>
+        <v>-10604.25</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1801,31 +1804,31 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>17272.85625000000073</v>
+        <v>34603.48124999999709</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
-        <v>-1733.0625</v>
+        <v>-2310.75</v>
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-11370.20624999999927</v>
+        <v>-21617.26875000000291</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-16956.95624999999927</v>
+        <v>-32221.51875000000291</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1846,31 +1849,31 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>25586.78484374999607</v>
+        <v>51259.14421874999243</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
-        <v>-2567.23593749999964</v>
+        <v>-3422.98124999999982</v>
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-3890.45109375000175</v>
+        <v>-6073.83703125000466</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-20847.40734375000102</v>
+        <v>-38295.35578125000757</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1891,31 +1894,31 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>33692.86522265624808</v>
+        <v>67498.41561328124953</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
-        <v>-3380.55503906249987</v>
+        <v>-4507.40671874999953</v>
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>3402.31018359374866</v>
+        <v>9081.0088945312527358</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-17445.097160156252357</v>
+        <v>-29214.34688671875483</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1936,31 +1939,31 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>41596.29359208983806</v>
+        <v>83331.70522294921102</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
-        <v>-4173.54116308593711</v>
+        <v>-5564.72155078124979</v>
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>10512.75242900390003</v>
+        <v>23856.98367216796032</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>-6932.34473115235232</v>
+        <v>-5357.36321455079451</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1981,31 +1984,31 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>49302.13625228759338</v>
+        <v>98769.16259237547638</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
-        <v>-4946.70263400878866</v>
+        <v>-6595.60351201171761</v>
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>17445.4336182788029</v>
+        <v>38263.55908036376059</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>10513.088887126450572</v>
+        <v>32906.19586581296608</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2026,31 +2029,31 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>56815.33284598040336</v>
+        <v>113820.6835275660851</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
-        <v>-5700.53506815856872</v>
+        <v>-7600.71342421142526</v>
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>24204.79777782183373</v>
+        <v>52309.97010335465893</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>34717.88666494828067</v>
+        <v>85216.16596916763228</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2071,31 +2074,31 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>64140.69952483088855</v>
+        <v>128495.91643937693152</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
-        <v>-6435.52169145460448</v>
+        <v>-8580.6955886061387</v>
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>30795.17783337628498</v>
+        <v>66005.22085077079828</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>65513.064498324565648</v>
+        <v>151221.38681993843056</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2116,31 +2119,31 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>71282.93203671011725</v>
+        <v>142804.26852839250932</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
-        <v>-7152.13364916823866</v>
+        <v>-9536.1781988909861</v>
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>37220.79838754187949</v>
+        <v>79358.090329501515953</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>102733.86288586644514</v>
+        <v>230579.47714943994652</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2161,31 +2164,31 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>78246.6087357923534</v>
+        <v>156754.91181518268422</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
-        <v>-7850.83030793903254</v>
+        <v>-10467.77374391871126</v>
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>43485.77842785332177</v>
+        <v>92377.13807126396568</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>146219.64131371976691</v>
+        <v>322956.6152207038831</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2206,31 +2209,31 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>85036.19351739755075</v>
+        <v>170356.78901980313822</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
-        <v>-8532.059550240557655</v>
+        <v>-11376.079400320742934</v>
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>49594.13396715698764</v>
+        <v>105070.7096194823971</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>195813.77528087675455</v>
+        <v>428027.3248401862802</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2251,31 +2254,31 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>91656.038679462610162</v>
+        <v>183618.61929430803866</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
-        <v>-9196.25806148454285</v>
+        <v>-12261.67741531272441</v>
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-13455</v>
+        <v>-26955</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-26910</v>
+        <v>-53910</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>55549.78061797807459</v>
+        <v>117446.94187899530516</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>251363.55589885482914</v>
+        <v>545474.26671918155625</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2289,7 +2292,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>20847.40734375000102</v>
+        <v>38295.35578125000757</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2298,7 +2301,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>31271.11101562499971</v>
+        <v>57443.03367187501135</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2307,7 +2310,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>91656.038679462610162</v>
+        <v>183618.61929430803866</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2316,7 +2319,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>55549.78061797807459</v>
+        <v>117446.94187899530516</v>
       </c>
     </row>
   </sheetData>
@@ -2380,7 +2383,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>599</v>
+        <v>1199</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -2402,7 +2405,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>1797</v>
+        <v>3597</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2417,7 +2420,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>898.5</v>
+        <v>1798.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2432,7 +2435,7 @@
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>898.5</v>
+        <v>1798.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2511,7 +2514,7 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>17520.75</v>
+        <v>35070.75</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
@@ -2519,22 +2522,22 @@
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-10896.75</v>
+        <v>-20346.75</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-10896.75</v>
+        <v>-20346.75</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2555,7 +2558,7 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>34603.48124999999709</v>
+        <v>69264.73124999999709</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
@@ -2563,23 +2566,23 @@
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-22194.95625000000291</v>
+        <v>-41533.70625000000291</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-33091.70625000000291</v>
+        <v>-61880.45625000000291</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2600,7 +2603,7 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>51259.14421874999243</v>
+        <v>102603.86296874999243</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
@@ -2608,23 +2611,23 @@
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-6929.58234375000757</v>
+        <v>-9584.86359375000757</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-40021.28859375001048</v>
+        <v>-71465.31984375001048</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2645,7 +2648,7 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>67498.41561328124953</v>
+        <v>135109.51639453123789</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
@@ -2653,23 +2656,23 @@
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>7954.15721484374808</v>
+        <v>21565.25799609374371</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-32067.1313789062624</v>
+        <v>-49900.061847656266764</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2690,7 +2693,7 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>83331.70522294921102</v>
+        <v>166802.52848466794239</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
@@ -2698,23 +2701,23 @@
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>22465.80328447265492</v>
+        <v>51936.62654619137174</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>-9601.32809443360748</v>
+        <v>2036.56469853510498</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2735,7 +2738,7 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>98769.16259237547638</v>
+        <v>197703.21527255122783</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
@@ -2743,23 +2746,23 @@
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>36614.65820236083528</v>
+        <v>81548.71088253657217</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>27013.3301079272278</v>
+        <v>83585.27558107167715</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2780,7 +2783,7 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>113820.6835275660851</v>
+        <v>227831.38489073747769</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
@@ -2788,23 +2791,23 @@
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>50409.79174730180239</v>
+        <v>110420.49311047320953</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>77423.12185522902291</v>
+        <v>194005.76869154488668</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2825,7 +2828,7 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>128495.91643937693152</v>
+        <v>257206.35026846901746</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
@@ -2833,23 +2836,23 @@
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>63860.046953619254055</v>
+        <v>138570.48078271135455</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>141283.16880884827697</v>
+        <v>332576.24947425624123</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2870,7 +2873,7 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>142804.26852839250932</v>
+        <v>285846.94151175726438</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
@@ -2878,23 +2881,23 @@
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>76974.045779778782162</v>
+        <v>166016.71876314352266</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>218257.21458862704458</v>
+        <v>498592.96823739976389</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2915,7 +2918,7 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>156754.91181518268422</v>
+        <v>313771.51797396334587</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
@@ -2923,23 +2926,23 @@
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>89760.19463528430788</v>
+        <v>192776.80079406494042</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>308017.40922391135246</v>
+        <v>691369.76903146470431</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2960,7 +2963,7 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>170356.78901980313822</v>
+        <v>340997.98002461425494</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
@@ -2968,23 +2971,23 @@
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>102226.68976940220455</v>
+        <v>218867.88077421335038</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>410244.098993313557003</v>
+        <v>910237.64980567805469</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3005,7 +3008,7 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>183618.61929430803866</v>
+        <v>367543.78052399889566</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
@@ -3013,23 +3016,23 @@
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-26955</v>
+        <v>-53955</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-53910</v>
+        <v>-107910</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>114381.52252516712178</v>
+        <v>244306.68375485797878</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>524625.62151848070789</v>
+        <v>1154544.33356053614989</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3043,7 +3046,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>40021.28859375001048</v>
+        <v>71465.31984375001048</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3052,7 +3055,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>60031.93289062501572</v>
+        <v>107197.97976562501572</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3061,7 +3064,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>183618.61929430803866</v>
+        <v>367543.78052399889566</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3070,7 +3073,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>114381.52252516712178</v>
+        <v>244306.68375485797878</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sales-cashflow.xlsx
+++ b/docs/sales-cashflow.xlsx
@@ -23,7 +23,7 @@
     <t>DocFácil — Corridas de caja del módulo de ventas</t>
   </si>
   <si>
-    <t>Parámetros: 3 vendedores × 10 ventas/mes · comisión 3× split 50/50 · churn 2.5% mensual</t>
+    <t>Parámetros: 3 vendedores × 10 ventas/mes · comisión 1.5× split 50/50 · churn 2.5% mensual</t>
   </si>
   <si>
     <t>Plan</t>
@@ -703,22 +703,22 @@
       </c>
       <c r="B5" s="6">
         <f>Básico!B4</f>
-        <v>299</v>
+        <v>149</v>
       </c>
       <c r="C5" s="6">
         <f>Básico!F28</f>
-        <v>20847.40734375000102</v>
+        <v>274.5</v>
       </c>
       <c r="D5" s="7">
         <f>Básico!F29</f>
-        <v>31271.11101562499971</v>
+        <v>411.75</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="6">
         <f>Básico!F31</f>
-        <v>55549.78061797807459</v>
+        <v>31306.19998746944475</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -727,22 +727,22 @@
       </c>
       <c r="B6" s="6">
         <f>Profesional!B4</f>
-        <v>599</v>
+        <v>299</v>
       </c>
       <c r="C6" s="6">
         <f>Profesional!F28</f>
-        <v>38295.35578125000757</v>
+        <v>994.5</v>
       </c>
       <c r="D6" s="7">
         <f>Profesional!F29</f>
-        <v>57443.03367187501135</v>
+        <v>1491.75</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="6">
         <f>Profesional!F31</f>
-        <v>117446.94187899530516</v>
+        <v>67472.0709410639829</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -751,22 +751,22 @@
       </c>
       <c r="B7" s="6">
         <f>Clínica!B4</f>
-        <v>1199</v>
+        <v>499</v>
       </c>
       <c r="C7" s="6">
         <f>Clínica!F28</f>
-        <v>71465.31984375001048</v>
+        <v>2052</v>
       </c>
       <c r="D7" s="7">
         <f>Clínica!F29</f>
-        <v>107197.97976562501572</v>
+        <v>3078</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="6">
         <f>Clínica!F31</f>
-        <v>244306.68375485797878</v>
+        <v>116715.038663799408823</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -875,7 +875,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>299</v>
+        <v>149</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>897</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -912,7 +912,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>448.5</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -920,14 +920,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>448.5</v>
+        <v>111.75</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -951,7 +951,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1006,30 +1006,30 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>8745.75</v>
+        <v>4358.25</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
-        <v>-877.5</v>
+        <v>-731.25</v>
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-5586.75</v>
+        <v>274.5</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-5586.75</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1050,31 +1050,31 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>17272.85625000000073</v>
+        <v>8607.54374999999891</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
-        <v>-1733.0625</v>
+        <v>-1444.21875</v>
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-11370.20624999999927</v>
+        <v>458.32499999999891</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-16956.95624999999927</v>
+        <v>732.82499999999891</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1095,31 +1095,31 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>25586.78484374999607</v>
+        <v>12750.60515624999971</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
-        <v>-2567.23593749999964</v>
+        <v>-2139.36328125</v>
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-3890.45109375000175</v>
+        <v>3906.24187499999971</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-20847.40734375000102</v>
+        <v>4639.066874999998618</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1140,31 +1140,31 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>33692.86522265624808</v>
+        <v>16790.090027343747352</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
-        <v>-3380.55503906249987</v>
+        <v>-2817.12919921874982</v>
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>3402.31018359374866</v>
+        <v>7267.96082812499662</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-17445.097160156252357</v>
+        <v>11907.027703124995242</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1185,31 +1185,31 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>41596.29359208983806</v>
+        <v>20728.58777666015521</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
-        <v>-4173.54116308593711</v>
+        <v>-3477.95096923828078</v>
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>10512.75242900390003</v>
+        <v>10545.63680742187353</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>-6932.34473115235232</v>
+        <v>22452.66451054687059</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1230,31 +1230,31 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>49302.13625228759338</v>
+        <v>24568.62308224364824</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
-        <v>-4946.70263400878866</v>
+        <v>-4122.25219500732328</v>
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>17445.4336182788029</v>
+        <v>13741.37088723632405</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>10513.088887126450572</v>
+        <v>36194.035397783198277</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1275,31 +1275,31 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>56815.33284598040336</v>
+        <v>28312.65750518755885</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
-        <v>-5700.53506815856872</v>
+        <v>-4750.44589013214045</v>
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>24204.79777782183373</v>
+        <v>16857.2116150554175</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>34717.88666494828067</v>
+        <v>53051.24701283861941</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1320,31 +1320,31 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>64140.69952483088855</v>
+        <v>31963.091067557870701</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
-        <v>-6435.52169145460448</v>
+        <v>-5362.93474287883691</v>
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>30795.17783337628498</v>
+        <v>19895.15632467903197</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>65513.064498324565648</v>
+        <v>72946.40333751765138</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1365,31 +1365,31 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>71282.93203671011725</v>
+        <v>35522.26379086892121</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
-        <v>-7152.13364916823866</v>
+        <v>-5960.11137430686631</v>
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>37220.79838754187949</v>
+        <v>22857.15241656205399</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>102733.86288586644514</v>
+        <v>95803.55575407970173</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1410,31 +1410,31 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>78246.6087357923534</v>
+        <v>38992.45719609719526</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
-        <v>-7850.83030793903254</v>
+        <v>-6542.35858994919363</v>
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>43485.77842785332177</v>
+        <v>25745.098606147999817</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>146219.64131371976691</v>
+        <v>121548.65436022769427</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1455,31 +1455,31 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>85036.19351739755075</v>
+        <v>42375.89576619477157</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
-        <v>-8532.059550240557655</v>
+        <v>-7110.049625200465016</v>
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>49594.13396715698764</v>
+        <v>28560.84614099430473</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>195813.77528087675455</v>
+        <v>150109.50050122200628</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1500,31 +1500,31 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>91656.038679462610162</v>
+        <v>45674.74837203989591</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
-        <v>-9196.25806148454285</v>
+        <v>-7663.54838457045298</v>
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-13455</v>
+        <v>-3352.5</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-26910</v>
+        <v>-6705</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>55549.78061797807459</v>
+        <v>31306.19998746944475</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>251363.55589885482914</v>
+        <v>181415.70048869145103</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>20847.40734375000102</v>
+        <v>274.5</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>31271.11101562499971</v>
+        <v>411.75</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>91656.038679462610162</v>
+        <v>45674.74837203989591</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>55549.78061797807459</v>
+        <v>31306.19998746944475</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1629,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>599</v>
+        <v>299</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>1797</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>898.5</v>
+        <v>224.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1674,14 +1674,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>898.5</v>
+        <v>224.25</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1705,7 +1705,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1760,30 +1760,30 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>17520.75</v>
+        <v>8745.75</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
-        <v>-1170</v>
+        <v>-1023.75</v>
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-10604.25</v>
+        <v>994.5</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-10604.25</v>
+        <v>994.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1804,31 +1804,31 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>34603.48124999999709</v>
+        <v>17272.85625000000073</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
-        <v>-2310.75</v>
+        <v>-2021.90625</v>
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-21617.26875000000291</v>
+        <v>1795.95000000000073</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-32221.51875000000291</v>
+        <v>2790.45000000000073</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1849,31 +1849,31 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>51259.14421874999243</v>
+        <v>25586.78484374999607</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
-        <v>-3422.98124999999982</v>
+        <v>-2995.10859374999973</v>
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-6073.83703125000466</v>
+        <v>9136.6762499999968</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-38295.35578125000757</v>
+        <v>11927.12624999999753</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1894,31 +1894,31 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>67498.41561328124953</v>
+        <v>33692.86522265624808</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
-        <v>-4507.40671874999953</v>
+        <v>-3943.98087890624993</v>
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>9081.0088945312527358</v>
+        <v>16293.88434374999633</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-29214.34688671875483</v>
+        <v>28221.010593749993859</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1939,31 +1939,31 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>83331.70522294921102</v>
+        <v>41596.29359208983806</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
-        <v>-5564.72155078124979</v>
+        <v>-4869.13135693359345</v>
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>23856.98367216796032</v>
+        <v>23272.16223515624733</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>-5357.36321455079451</v>
+        <v>51493.17282890624483</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1984,31 +1984,31 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>98769.16259237547638</v>
+        <v>49302.13625228759338</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
-        <v>-6595.60351201171761</v>
+        <v>-5771.15307301025314</v>
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>38263.55908036376059</v>
+        <v>30075.98317927734024</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>32906.19586581296608</v>
+        <v>81569.1560081835778</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2029,31 +2029,31 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>113820.6835275660851</v>
+        <v>56815.33284598040336</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
-        <v>-7600.71342421142526</v>
+        <v>-6650.62424618499699</v>
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>52309.97010335465893</v>
+        <v>36709.70859979540546</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>85216.16596916763228</v>
+        <v>118278.86460797899053</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2074,31 +2074,31 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>128495.91643937693152</v>
+        <v>64140.69952483088855</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
-        <v>-8580.6955886061387</v>
+        <v>-7508.10864003037204</v>
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>66005.22085077079828</v>
+        <v>43177.59088480052014</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>151221.38681993843056</v>
+        <v>161456.45549277949613</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2119,31 +2119,31 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>142804.26852839250932</v>
+        <v>71282.93203671011725</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
-        <v>-9536.1781988909861</v>
+        <v>-8344.15592402961192</v>
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>79358.090329501515953</v>
+        <v>49483.77611268050532</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>230579.47714943994652</v>
+        <v>210940.23160545999417</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2164,31 +2164,31 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>156754.91181518268422</v>
+        <v>78246.6087357923534</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
-        <v>-10467.77374391871126</v>
+        <v>-9159.30202592887144</v>
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>92377.13807126396568</v>
+        <v>55632.30670986347832</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>322956.6152207038831</v>
+        <v>266572.53831532347249</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2209,31 +2209,31 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>170356.78901980313822</v>
+        <v>85036.19351739755075</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
-        <v>-11376.079400320742934</v>
+        <v>-9954.069475280650295</v>
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>105070.7096194823971</v>
+        <v>61627.12404211690591</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>428027.3248401862802</v>
+        <v>328199.66235744039295</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2254,31 +2254,31 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>183618.61929430803866</v>
+        <v>91656.038679462610162</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
-        <v>-12261.67741531272441</v>
+        <v>-10728.96773839863454</v>
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-26955</v>
+        <v>-6727.5</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-53910</v>
+        <v>-13455</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>117446.94187899530516</v>
+        <v>67472.0709410639829</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>545474.26671918155625</v>
+        <v>395671.73329850437585</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>38295.35578125000757</v>
+        <v>994.5</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>57443.03367187501135</v>
+        <v>1491.75</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>183618.61929430803866</v>
+        <v>91656.038679462610162</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>117446.94187899530516</v>
+        <v>67472.0709410639829</v>
       </c>
     </row>
   </sheetData>
@@ -2383,7 +2383,7 @@
         <v>22</v>
       </c>
       <c r="B4" s="12">
-        <v>1199</v>
+        <v>499</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>3597</v>
+        <v>748.5</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>1798.5</v>
+        <v>374.25</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2428,14 +2428,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>1798.5</v>
+        <v>374.25</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2459,7 +2459,7 @@
         <v>28</v>
       </c>
       <c r="B10" s="12">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2514,30 +2514,30 @@
       </c>
       <c r="E14" s="17">
         <f>D14*$B$4</f>
-        <v>35070.75</v>
+        <v>14595.75</v>
       </c>
       <c r="F14" s="17">
         <f>-D14*$B$10</f>
-        <v>-1462.5</v>
+        <v>-1316.25</v>
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>-20346.75</v>
+        <v>2052</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>-20346.75</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2558,31 +2558,31 @@
       </c>
       <c r="E15" s="17">
         <f>D15*$B$4</f>
-        <v>69264.73124999999709</v>
+        <v>28826.60624999999709</v>
       </c>
       <c r="F15" s="17">
         <f>-D15*$B$10</f>
-        <v>-2888.4375</v>
+        <v>-2599.59375</v>
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>-41533.70625000000291</v>
+        <v>3772.01249999999709</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>-61880.45625000000291</v>
+        <v>5824.01249999999709</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2603,31 +2603,31 @@
       </c>
       <c r="E16" s="17">
         <f>D16*$B$4</f>
-        <v>102603.86296874999243</v>
+        <v>42701.69109374999971</v>
       </c>
       <c r="F16" s="17">
         <f>-D16*$B$10</f>
-        <v>-4278.7265625</v>
+        <v>-3850.85390624999945</v>
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>-9584.86359375000757</v>
+        <v>16395.83718750000116</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>-71465.31984375001048</v>
+        <v>22219.84968749999825</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2648,31 +2648,31 @@
       </c>
       <c r="E17" s="17">
         <f>D17*$B$4</f>
-        <v>135109.51639453123789</v>
+        <v>56229.89881640624662</v>
       </c>
       <c r="F17" s="17">
         <f>-D17*$B$10</f>
-        <v>-5634.25839843749964</v>
+        <v>-5070.83255859375004</v>
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>21565.25799609374371</v>
+        <v>28704.066257812497497</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>-49900.061847656266764</v>
+        <v>50923.91594531249575</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2693,31 +2693,31 @@
       </c>
       <c r="E18" s="17">
         <f>D18*$B$4</f>
-        <v>166802.52848466794239</v>
+        <v>69419.90134599608427</v>
       </c>
       <c r="F18" s="17">
         <f>-D18*$B$10</f>
-        <v>-6955.90193847656155</v>
+        <v>-6260.31174462890613</v>
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>51936.62654619137174</v>
+        <v>40704.58960136718088</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>2036.56469853510498</v>
+        <v>91628.50554667967663</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2738,31 +2738,31 @@
       </c>
       <c r="E19" s="17">
         <f>D19*$B$4</f>
-        <v>197703.21527255122783</v>
+        <v>82280.15381234617962</v>
       </c>
       <c r="F19" s="17">
         <f>-D19*$B$10</f>
-        <v>-8244.50439001464656</v>
+        <v>-7420.053951013182996</v>
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>81548.71088253657217</v>
+        <v>52405.099861333001172</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>83585.27558107167715</v>
+        <v>144033.60540801269235</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2783,31 +2783,31 @@
       </c>
       <c r="E20" s="17">
         <f>D20*$B$4</f>
-        <v>227831.38489073747769</v>
+        <v>94818.89996703753422</v>
       </c>
       <c r="F20" s="17">
         <f>-D20*$B$10</f>
-        <v>-9500.8917802642809</v>
+        <v>-8550.80260223785262</v>
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>110420.49311047320953</v>
+        <v>63813.097364799687057</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>194005.76869154488668</v>
+        <v>207846.70277281239396</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2828,31 +2828,31 @@
       </c>
       <c r="E21" s="17">
         <f>D21*$B$4</f>
-        <v>257206.35026846901746</v>
+        <v>107044.17746786159114</v>
       </c>
       <c r="F21" s="17">
         <f>-D21*$B$10</f>
-        <v>-10725.86948575767383</v>
+        <v>-9653.28253718190717</v>
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>138570.48078271135455</v>
+        <v>74935.89493067968579</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>332576.24947425624123</v>
+        <v>282782.5977034920943</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2873,31 +2873,31 @@
       </c>
       <c r="E22" s="17">
         <f>D22*$B$4</f>
-        <v>285846.94151175726438</v>
+        <v>118963.82303116504045</v>
       </c>
       <c r="F22" s="17">
         <f>-D22*$B$10</f>
-        <v>-11920.22274861373262</v>
+        <v>-10728.20047375235845</v>
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>166016.71876314352266</v>
+        <v>85780.62255741268746</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>498592.96823739976389</v>
+        <v>368563.22026090475265</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2918,31 +2918,31 @@
       </c>
       <c r="E23" s="17">
         <f>D23*$B$4</f>
-        <v>313771.51797396334587</v>
+        <v>130585.47745538591698</v>
       </c>
       <c r="F23" s="17">
         <f>-D23*$B$10</f>
-        <v>-13084.71717989838726</v>
+        <v>-11776.24546190854926</v>
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>192776.80079406494042</v>
+        <v>96354.23199347736954</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>691369.76903146470431</v>
+        <v>464917.45225438213674</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2963,31 +2963,31 @@
       </c>
       <c r="E24" s="17">
         <f>D24*$B$4</f>
-        <v>340997.98002461425494</v>
+        <v>141916.59051900127088</v>
       </c>
       <c r="F24" s="17">
         <f>-D24*$B$10</f>
-        <v>-14220.099250400930032</v>
+        <v>-12798.089325360835574</v>
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>218867.88077421335038</v>
+        <v>106663.50119364043348</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>910237.64980567805469</v>
+        <v>571580.95344802259933</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3008,31 +3008,31 @@
       </c>
       <c r="E25" s="17">
         <f>D25*$B$4</f>
-        <v>367543.78052399889566</v>
+        <v>152964.42575602623401</v>
       </c>
       <c r="F25" s="17">
         <f>-D25*$B$10</f>
-        <v>-15327.096769140905963</v>
+        <v>-13794.38709222681427</v>
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-53955</v>
+        <v>-11227.5</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-107910</v>
+        <v>-22455</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>244306.68375485797878</v>
+        <v>116715.038663799408823</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>1154544.33356053614989</v>
+        <v>688295.99211182200816</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>71465.31984375001048</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>107197.97976562501572</v>
+        <v>3078</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3064,7 +3064,7 @@
       </c>
       <c r="F30" s="19">
         <f>E25</f>
-        <v>367543.78052399889566</v>
+        <v>152964.42575602623401</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>244306.68375485797878</v>
+        <v>116715.038663799408823</v>
       </c>
     </row>
   </sheetData>

--- a/docs/sales-cashflow.xlsx
+++ b/docs/sales-cashflow.xlsx
@@ -23,7 +23,7 @@
     <t>DocFácil — Corridas de caja del módulo de ventas</t>
   </si>
   <si>
-    <t>Parámetros: 3 vendedores × 10 ventas/mes · comisión 1.5× split 50/50 · churn 2.5% mensual</t>
+    <t>Parámetros: 3 vendedores × 10 ventas/mes · comisión 3× split 50/50 · churn 2.5% mensual</t>
   </si>
   <si>
     <t>Plan</t>
@@ -707,18 +707,18 @@
       </c>
       <c r="C5" s="6">
         <f>Básico!F28</f>
-        <v>274.5</v>
+        <v>12123.43312500000138</v>
       </c>
       <c r="D5" s="7">
         <f>Básico!F29</f>
-        <v>411.75</v>
+        <v>18185.14968750000116</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="6">
         <f>Básico!F31</f>
-        <v>31306.19998746944475</v>
+        <v>24601.19998746944475</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -731,18 +731,18 @@
       </c>
       <c r="C6" s="6">
         <f>Profesional!F28</f>
-        <v>994.5</v>
+        <v>21710.37375000000247</v>
       </c>
       <c r="D6" s="7">
         <f>Profesional!F29</f>
-        <v>1491.75</v>
+        <v>32565.56062500000553</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F6" s="6">
         <f>Profesional!F31</f>
-        <v>67472.0709410639829</v>
+        <v>54017.0709410639829</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -755,18 +755,18 @@
       </c>
       <c r="C7" s="6">
         <f>Clínica!F28</f>
-        <v>2052</v>
+        <v>33917.65031250000175</v>
       </c>
       <c r="D7" s="7">
         <f>Clínica!F29</f>
-        <v>3078</v>
+        <v>50876.47546875000262</v>
       </c>
       <c r="E7" s="8" t="s">
         <v>9</v>
       </c>
       <c r="F7" s="6">
         <f>Clínica!F31</f>
-        <v>116715.038663799408823</v>
+        <v>94260.038663799408823</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -897,7 +897,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>223.5</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -912,7 +912,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>111.75</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -920,14 +920,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>111.75</v>
+        <v>223.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1014,22 +1014,22 @@
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>274.5</v>
+        <v>-3078</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>274.5</v>
+        <v>-3078</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1058,23 +1058,23 @@
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>458.32499999999891</v>
+        <v>-6246.67500000000109</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>732.82499999999891</v>
+        <v>-9324.67500000000109</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1103,23 +1103,23 @@
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>3906.24187499999971</v>
+        <v>-2798.75812500000029</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>4639.066874999998618</v>
+        <v>-12123.43312500000138</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1148,23 +1148,23 @@
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>7267.96082812499662</v>
+        <v>562.96082812499662</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>11907.027703124995242</v>
+        <v>-11560.47229687500476</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1193,23 +1193,23 @@
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>10545.63680742187353</v>
+        <v>3840.63680742187353</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>22452.66451054687059</v>
+        <v>-7719.83548945313123</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1238,23 +1238,23 @@
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>13741.37088723632405</v>
+        <v>7036.37088723632405</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>36194.035397783198277</v>
+        <v>-683.46460221680718</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1283,23 +1283,23 @@
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>16857.2116150554175</v>
+        <v>10152.2116150554175</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>53051.24701283861941</v>
+        <v>9468.74701283861032</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1328,23 +1328,23 @@
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>19895.15632467903197</v>
+        <v>13190.15632467903197</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>72946.40333751765138</v>
+        <v>22658.9033375176441</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1373,23 +1373,23 @@
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>22857.15241656205399</v>
+        <v>16152.15241656205399</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>95803.55575407970173</v>
+        <v>38811.055754079701728</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1418,23 +1418,23 @@
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>25745.098606147999817</v>
+        <v>19040.098606147999817</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>121548.65436022769427</v>
+        <v>57851.15436022770155</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1463,23 +1463,23 @@
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>28560.84614099430473</v>
+        <v>21855.84614099430473</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>150109.50050122200628</v>
+        <v>79707.00050122200627811</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1508,23 +1508,23 @@
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-3352.5</v>
+        <v>-6705</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-6705</v>
+        <v>-13410</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>31306.19998746944475</v>
+        <v>24601.19998746944475</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>181415.70048869145103</v>
+        <v>104308.20048869145103</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>274.5</v>
+        <v>12123.43312500000138</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>411.75</v>
+        <v>18185.14968750000116</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1565,7 +1565,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>31306.19998746944475</v>
+        <v>24601.19998746944475</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>448.5</v>
+        <v>897</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>224.25</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1674,14 +1674,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>224.25</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1768,22 +1768,22 @@
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>994.5</v>
+        <v>-5733</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>994.5</v>
+        <v>-5733</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1812,23 +1812,23 @@
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>1795.95000000000073</v>
+        <v>-11659.049999999999272</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>2790.45000000000073</v>
+        <v>-17392.049999999999272</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1857,23 +1857,23 @@
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>9136.6762499999968</v>
+        <v>-4318.3237500000032</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>11927.12624999999753</v>
+        <v>-21710.37375000000247</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1902,23 +1902,23 @@
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>16293.88434374999633</v>
+        <v>2838.88434374999633</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>28221.010593749993859</v>
+        <v>-18871.48940625000614</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1947,23 +1947,23 @@
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>23272.16223515624733</v>
+        <v>9817.16223515624733</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>51493.17282890624483</v>
+        <v>-9054.32717109375881</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1992,23 +1992,23 @@
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>30075.98317927734024</v>
+        <v>16620.98317927734024</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>81569.1560081835778</v>
+        <v>7566.65600818358143</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2037,23 +2037,23 @@
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>36709.70859979540546</v>
+        <v>23254.70859979540546</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>118278.86460797899053</v>
+        <v>30821.3646079789869</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2082,23 +2082,23 @@
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>43177.59088480052014</v>
+        <v>29722.59088480052014</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>161456.45549277949613</v>
+        <v>60543.95549277951068</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2127,23 +2127,23 @@
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>49483.77611268050532</v>
+        <v>36028.77611268050532</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>210940.23160545999417</v>
+        <v>96572.73160546002327</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2172,23 +2172,23 @@
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>55632.30670986347832</v>
+        <v>42177.30670986347832</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>266572.53831532347249</v>
+        <v>138750.038315323501593</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2217,23 +2217,23 @@
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>61627.12404211690591</v>
+        <v>48172.12404211690591</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>328199.66235744039295</v>
+        <v>186922.16235744039295</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -2262,23 +2262,23 @@
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-6727.5</v>
+        <v>-13455</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-13455</v>
+        <v>-26910</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>67472.0709410639829</v>
+        <v>54017.0709410639829</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>395671.73329850437585</v>
+        <v>240939.23329850437585</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>994.5</v>
+        <v>21710.37375000000247</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>1491.75</v>
+        <v>32565.56062500000553</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>67472.0709410639829</v>
+        <v>54017.0709410639829</v>
       </c>
     </row>
   </sheetData>
@@ -2405,7 +2405,7 @@
       </c>
       <c r="E5" s="15">
         <f>B4*B7</f>
-        <v>748.5</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="E6" s="15">
         <f>E5*B8</f>
-        <v>374.25</v>
+        <v>748.5</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2428,14 +2428,14 @@
         <v>25</v>
       </c>
       <c r="B7" s="11">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
       </c>
       <c r="E7" s="15">
         <f>E5*(1-B8)</f>
-        <v>374.25</v>
+        <v>748.5</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2522,22 +2522,22 @@
       </c>
       <c r="G14" s="17">
         <f>-C14*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H14" s="17">
         <v>0</v>
       </c>
       <c r="I14" s="17">
         <f>G14+H14</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="J14" s="17">
         <f>E14+F14+I14</f>
-        <v>2052</v>
+        <v>-9175.5</v>
       </c>
       <c r="K14" s="17">
         <f>J14</f>
-        <v>2052</v>
+        <v>-9175.5</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2566,23 +2566,23 @@
       </c>
       <c r="G15" s="17">
         <f>-C15*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H15" s="17">
         <f>-C14*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I15" s="17">
         <f>G15+H15</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J15" s="17">
         <f>E15+F15+I15</f>
-        <v>3772.01249999999709</v>
+        <v>-18682.98750000000291</v>
       </c>
       <c r="K15" s="17">
         <f>K14+J15</f>
-        <v>5824.01249999999709</v>
+        <v>-27858.48750000000291</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2611,23 +2611,23 @@
       </c>
       <c r="G16" s="17">
         <f>-C16*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H16" s="17">
         <f>-C15*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I16" s="17">
         <f>G16+H16</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J16" s="17">
         <f>E16+F16+I16</f>
-        <v>16395.83718750000116</v>
+        <v>-6059.16281249999884</v>
       </c>
       <c r="K16" s="17">
         <f>K15+J16</f>
-        <v>22219.84968749999825</v>
+        <v>-33917.65031250000175</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2656,23 +2656,23 @@
       </c>
       <c r="G17" s="17">
         <f>-C17*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H17" s="17">
         <f>-C16*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I17" s="17">
         <f>G17+H17</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J17" s="17">
         <f>E17+F17+I17</f>
-        <v>28704.066257812497497</v>
+        <v>6249.066257812497497</v>
       </c>
       <c r="K17" s="17">
         <f>K16+J17</f>
-        <v>50923.91594531249575</v>
+        <v>-27668.58405468750425</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2701,23 +2701,23 @@
       </c>
       <c r="G18" s="17">
         <f>-C18*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H18" s="17">
         <f>-C17*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I18" s="17">
         <f>G18+H18</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J18" s="17">
         <f>E18+F18+I18</f>
-        <v>40704.58960136718088</v>
+        <v>18249.58960136718088</v>
       </c>
       <c r="K18" s="17">
         <f>K17+J18</f>
-        <v>91628.50554667967663</v>
+        <v>-9418.99445332032337</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2746,23 +2746,23 @@
       </c>
       <c r="G19" s="17">
         <f>-C19*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H19" s="17">
         <f>-C18*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I19" s="17">
         <f>G19+H19</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J19" s="17">
         <f>E19+F19+I19</f>
-        <v>52405.099861333001172</v>
+        <v>29950.099861333001172</v>
       </c>
       <c r="K19" s="17">
         <f>K18+J19</f>
-        <v>144033.60540801269235</v>
+        <v>20531.1054080126778</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2791,23 +2791,23 @@
       </c>
       <c r="G20" s="17">
         <f>-C20*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H20" s="17">
         <f>-C19*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I20" s="17">
         <f>G20+H20</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J20" s="17">
         <f>E20+F20+I20</f>
-        <v>63813.097364799687057</v>
+        <v>41358.097364799687057</v>
       </c>
       <c r="K20" s="17">
         <f>K19+J20</f>
-        <v>207846.70277281239396</v>
+        <v>61889.20277281236486</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -2836,23 +2836,23 @@
       </c>
       <c r="G21" s="17">
         <f>-C21*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H21" s="17">
         <f>-C20*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I21" s="17">
         <f>G21+H21</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J21" s="17">
         <f>E21+F21+I21</f>
-        <v>74935.89493067968579</v>
+        <v>52480.89493067968579</v>
       </c>
       <c r="K21" s="17">
         <f>K20+J21</f>
-        <v>282782.5977034920943</v>
+        <v>114370.097703492050641</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2881,23 +2881,23 @@
       </c>
       <c r="G22" s="17">
         <f>-C22*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H22" s="17">
         <f>-C21*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I22" s="17">
         <f>G22+H22</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J22" s="17">
         <f>E22+F22+I22</f>
-        <v>85780.62255741268746</v>
+        <v>63325.62255741268746</v>
       </c>
       <c r="K22" s="17">
         <f>K21+J22</f>
-        <v>368563.22026090475265</v>
+        <v>177695.72026090475265</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -2926,23 +2926,23 @@
       </c>
       <c r="G23" s="17">
         <f>-C23*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H23" s="17">
         <f>-C22*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I23" s="17">
         <f>G23+H23</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J23" s="17">
         <f>E23+F23+I23</f>
-        <v>96354.23199347736954</v>
+        <v>73899.23199347736954</v>
       </c>
       <c r="K23" s="17">
         <f>K22+J23</f>
-        <v>464917.45225438213674</v>
+        <v>251594.95225438213674</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -2971,23 +2971,23 @@
       </c>
       <c r="G24" s="17">
         <f>-C24*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H24" s="17">
         <f>-C23*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I24" s="17">
         <f>G24+H24</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J24" s="17">
         <f>E24+F24+I24</f>
-        <v>106663.50119364043348</v>
+        <v>84208.50119364043348</v>
       </c>
       <c r="K24" s="17">
         <f>K23+J24</f>
-        <v>571580.95344802259933</v>
+        <v>335803.45344802259933</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -3016,23 +3016,23 @@
       </c>
       <c r="G25" s="17">
         <f>-C25*$E$6</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="H25" s="17">
         <f>-C24*$E$7</f>
-        <v>-11227.5</v>
+        <v>-22455</v>
       </c>
       <c r="I25" s="17">
         <f>G25+H25</f>
-        <v>-22455</v>
+        <v>-44910</v>
       </c>
       <c r="J25" s="17">
         <f>E25+F25+I25</f>
-        <v>116715.038663799408823</v>
+        <v>94260.038663799408823</v>
       </c>
       <c r="K25" s="17">
         <f>K24+J25</f>
-        <v>688295.99211182200816</v>
+        <v>430063.49211182200816</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -3046,7 +3046,7 @@
       </c>
       <c r="F28" s="19">
         <f>ABS(MIN(K14:K25))</f>
-        <v>2052</v>
+        <v>33917.65031250000175</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F29" s="20">
         <f>F28*1.5</f>
-        <v>3078</v>
+        <v>50876.47546875000262</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F31" s="19">
         <f>J25</f>
-        <v>116715.038663799408823</v>
+        <v>94260.038663799408823</v>
       </c>
     </row>
   </sheetData>
